--- a/data/trans_orig/IP07A12-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A12-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>10251</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20944</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14487</t>
+          <t>14970</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>25271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27467</t>
+          <t>27823</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42355</t>
+          <t>42212</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,57%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>12482</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24006</t>
+          <t>23859</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>11296</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21144</t>
+          <t>21210</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26994</t>
+          <t>26982</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42537</t>
+          <t>41569</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17861</t>
+          <t>19031</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24696</t>
+          <t>24473</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14948</t>
+          <t>14830</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14012</t>
+          <t>14449</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26458</t>
+          <t>26250</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17297</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11789</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20665</t>
+          <t>20939</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>23254</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35975</t>
+          <t>35604</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>57,74%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>15769</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>17255</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>11537</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22145</t>
+          <t>22330</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22470</t>
+          <t>22758</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35646</t>
+          <t>37606</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20512</t>
+          <t>20195</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>14700</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25610</t>
+          <t>25915</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28322</t>
+          <t>28852</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42568</t>
+          <t>43428</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>49,61%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7707</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20093</t>
+          <t>20693</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13166</t>
+          <t>12820</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25613</t>
+          <t>25190</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>709</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19601</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33292</t>
+          <t>33390</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15325</t>
+          <t>15721</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28610</t>
+          <t>28825</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38280</t>
+          <t>38048</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57694</t>
+          <t>57316</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31343</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46153</t>
+          <t>46675</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35528</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50605</t>
+          <t>50829</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>70802</t>
+          <t>71129</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>92641</t>
+          <t>92679</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,81%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14085</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>27022</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17940</t>
+          <t>18051</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>31072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35341</t>
+          <t>34937</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53049</t>
+          <t>53128</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18388</t>
+          <t>19192</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15392</t>
+          <t>15208</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27148</t>
+          <t>27300</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27235</t>
+          <t>27271</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>42268</t>
+          <t>43220</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>12507</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23810</t>
+          <t>23981</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>24016</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37473</t>
+          <t>37517</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>40213</t>
+          <t>39273</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>57794</t>
+          <t>57394</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,3%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12708</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24419</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22085</t>
+          <t>21544</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>26284</t>
+          <t>25933</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>41943</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>784</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>814</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12470</t>
+          <t>13182</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14694</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>12561</t>
+          <t>12699</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>25025</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>24384</t>
+          <t>24586</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17763</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>25757</t>
+          <t>24670</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>39597</t>
+          <t>38317</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>49,35%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>16874</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15204</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>16371</t>
+          <t>16692</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>29060</t>
+          <t>29192</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,6%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>538</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7626</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>5654</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>71855</t>
+          <t>73859</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>96892</t>
+          <t>98221</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>86096</t>
+          <t>86147</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>112872</t>
+          <t>112938</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>164693</t>
+          <t>166094</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>203368</t>
+          <t>203457</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>110256</t>
+          <t>109121</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>136069</t>
+          <t>137711</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>123746</t>
+          <t>125237</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>153627</t>
+          <t>152957</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>240961</t>
+          <t>240654</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>282316</t>
+          <t>280715</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>59456</t>
+          <t>60008</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>83442</t>
+          <t>84044</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>61943</t>
+          <t>63667</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>87398</t>
+          <t>87175</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>128102</t>
+          <t>129691</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>163197</t>
+          <t>163405</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>16394</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>14141</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>12324</t>
+          <t>12756</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>26236</t>
+          <t>26660</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>19247</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17913</t>
+          <t>18143</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28503</t>
+          <t>28559</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>11343</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19900</t>
+          <t>20365</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32088</t>
+          <t>32713</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46358</t>
+          <t>46248</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,17%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>15602</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18293</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17201</t>
+          <t>17696</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30487</t>
+          <t>29826</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15090</t>
+          <t>14932</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>583</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14183</t>
+          <t>14018</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23940</t>
+          <t>23883</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16986</t>
+          <t>16716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34117</t>
+          <t>33747</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47467</t>
+          <t>46881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>17915</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12795</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15186</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27165</t>
+          <t>27398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>9835</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19142</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>15317</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17731</t>
+          <t>17277</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31347</t>
+          <t>30110</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13879</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24844</t>
+          <t>24705</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>9071</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>25911</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40201</t>
+          <t>39689</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22887</t>
+          <t>23349</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30012</t>
+          <t>30115</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45043</t>
+          <t>44862</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33273</t>
+          <t>33842</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49487</t>
+          <t>49618</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67986</t>
+          <t>68258</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90784</t>
+          <t>89856</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,05%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22337</t>
+          <t>22127</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36613</t>
+          <t>36996</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21422</t>
+          <t>22846</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37585</t>
+          <t>37610</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47184</t>
+          <t>48034</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>68588</t>
+          <t>69275</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>12015</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24525</t>
+          <t>24556</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13380</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25625</t>
+          <t>25799</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28352</t>
+          <t>28603</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>46044</t>
+          <t>47112</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12135</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15426</t>
+          <t>14987</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7580</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17743</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30673</t>
+          <t>30832</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15346</t>
+          <t>15252</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27743</t>
+          <t>28359</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>37112</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>55487</t>
+          <t>55562</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36937</t>
+          <t>37295</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17289</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31064</t>
+          <t>31188</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>44916</t>
+          <t>44284</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>63776</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,85%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24123</t>
+          <t>24163</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13291</t>
+          <t>13622</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25557</t>
+          <t>25887</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>27498</t>
+          <t>28660</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>45312</t>
+          <t>46067</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>688</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14423</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19020</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>17591</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>30049</t>
+          <t>29777</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12593</t>
+          <t>11902</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21717</t>
+          <t>21822</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16238</t>
+          <t>15928</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28923</t>
+          <t>28494</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,22%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>7189</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>723</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>575</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>111935</t>
+          <t>113381</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>140699</t>
+          <t>141847</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>109887</t>
+          <t>111141</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>138831</t>
+          <t>139583</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>232458</t>
+          <t>232589</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>272915</t>
+          <t>272624</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>94263</t>
+          <t>93503</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>120110</t>
+          <t>120695</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>92570</t>
+          <t>92004</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>119675</t>
+          <t>119005</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>194737</t>
+          <t>191986</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>231054</t>
+          <t>230719</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,41%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>48292</t>
+          <t>49289</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>71425</t>
+          <t>72115</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>45973</t>
+          <t>46670</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>67374</t>
+          <t>68365</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>100827</t>
+          <t>100385</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>132263</t>
+          <t>132554</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16299</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>24400</t>
+          <t>23867</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>18886</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>35835</t>
+          <t>36180</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>13967</t>
+          <t>14187</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>16562</t>
+          <t>17420</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20852</t>
+          <t>20904</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>13540</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23341</t>
+          <t>24252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27498</t>
+          <t>27611</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40920</t>
+          <t>41214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,53%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17776</t>
+          <t>17442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19264</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32729</t>
+          <t>32626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,75%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12508</t>
+          <t>12616</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>599</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>759</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>488</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>985</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21559</t>
+          <t>21185</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14539</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26436</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28628</t>
+          <t>28481</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44085</t>
+          <t>44412</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,26%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>16235</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28331</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11044</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21933</t>
+          <t>22754</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30627</t>
+          <t>30780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46752</t>
+          <t>46965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15855</t>
+          <t>15719</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15985</t>
+          <t>15651</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14064</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27579</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>641</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19542</t>
+          <t>20196</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>13867</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26835</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,27%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16874</t>
+          <t>16829</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22117</t>
+          <t>21610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22448</t>
+          <t>22492</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35978</t>
+          <t>35785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20516</t>
+          <t>20599</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28572</t>
+          <t>28786</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45113</t>
+          <t>44782</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32448</t>
+          <t>32525</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49033</t>
+          <t>49187</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64468</t>
+          <t>65012</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88331</t>
+          <t>88355</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25115</t>
+          <t>24666</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41119</t>
+          <t>40191</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>29586</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43735</t>
+          <t>43867</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>65720</t>
+          <t>64521</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24008</t>
+          <t>23484</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39380</t>
+          <t>38855</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>29908</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46836</t>
+          <t>45478</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>57713</t>
+          <t>57733</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>80789</t>
+          <t>80588</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18445</t>
+          <t>17657</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20830</t>
+          <t>20159</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26906</t>
+          <t>26427</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12740</t>
+          <t>13539</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>26526</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29123</t>
+          <t>30431</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>47962</t>
+          <t>48824</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15348</t>
+          <t>15065</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27777</t>
+          <t>27794</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15133</t>
+          <t>14939</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27887</t>
+          <t>27463</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32349</t>
+          <t>33360</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>50296</t>
+          <t>50261</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19195</t>
+          <t>18853</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32890</t>
+          <t>32389</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13512</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25951</t>
+          <t>26327</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>35896</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>54386</t>
+          <t>55187</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>19532</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>11563</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>25002</t>
+          <t>25180</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9855</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11635</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18710</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>14940</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>28175</t>
+          <t>27419</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12563</t>
+          <t>12859</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9888</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20523</t>
+          <t>20312</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>16805</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>30825</t>
+          <t>29914</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>9193</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>18861</t>
+          <t>18704</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12718</t>
+          <t>12632</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>15877</t>
+          <t>15737</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>29122</t>
+          <t>28832</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>85193</t>
+          <t>86274</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>113643</t>
+          <t>114642</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>111616</t>
+          <t>112732</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>141997</t>
+          <t>142308</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>205404</t>
+          <t>206380</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>245133</t>
+          <t>250420</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>94274</t>
+          <t>94147</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>123297</t>
+          <t>123517</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>91399</t>
+          <t>90010</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>117540</t>
+          <t>117736</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>193324</t>
+          <t>190326</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>230491</t>
+          <t>233034</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>75217</t>
+          <t>76195</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>102788</t>
+          <t>103472</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>75665</t>
+          <t>74676</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>103965</t>
+          <t>102652</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>160405</t>
+          <t>160078</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>200577</t>
+          <t>198900</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>20227</t>
+          <t>20480</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>37788</t>
+          <t>38206</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>28584</t>
+          <t>28799</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>35971</t>
+          <t>36218</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>60216</t>
+          <t>59700</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>8559</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>20536</t>
+          <t>20786</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>8241</t>
+          <t>8972</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>12145</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>25683</t>
+          <t>25311</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
